--- a/AAII_Financials/Yearly/CNTM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CNTM_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>CNTM</t>
   </si>
@@ -715,10 +715,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>35800</v>
+        <v>33100</v>
       </c>
       <c r="E8" s="3">
-        <v>22700</v>
+        <v>21100</v>
       </c>
       <c r="F8" s="3">
         <v>20000</v>
@@ -748,10 +748,10 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>24400</v>
+        <v>22100</v>
       </c>
       <c r="E9" s="3">
-        <v>16700</v>
+        <v>15600</v>
       </c>
       <c r="F9" s="3">
         <v>14900</v>
@@ -781,10 +781,10 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>11500</v>
+        <v>10900</v>
       </c>
       <c r="E10" s="3">
-        <v>5900</v>
+        <v>5500</v>
       </c>
       <c r="F10" s="3">
         <v>5000</v>
@@ -895,7 +895,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-1100</v>
+        <v>900</v>
       </c>
       <c r="E14" s="3">
         <v>1700</v>
@@ -928,10 +928,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="F15" s="3">
         <v>900</v>
@@ -973,10 +973,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>47900</v>
+        <v>44500</v>
       </c>
       <c r="E17" s="3">
-        <v>31900</v>
+        <v>29900</v>
       </c>
       <c r="F17" s="3">
         <v>27300</v>
@@ -1006,10 +1006,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-12000</v>
+        <v>-11400</v>
       </c>
       <c r="E18" s="3">
-        <v>-9200</v>
+        <v>-8900</v>
       </c>
       <c r="F18" s="3">
         <v>-7300</v>
@@ -1054,7 +1054,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="E20" s="3">
         <v>8900</v>
@@ -1087,10 +1087,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-15000</v>
+        <v>-14500</v>
       </c>
       <c r="E21" s="3">
-        <v>-17300</v>
+        <v>-17000</v>
       </c>
       <c r="F21" s="3">
         <v>-6300</v>
@@ -1120,7 +1120,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="E22" s="3">
         <v>2700</v>
@@ -1153,10 +1153,10 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-16100</v>
+        <v>-17300</v>
       </c>
       <c r="E23" s="3">
-        <v>-22500</v>
+        <v>-22200</v>
       </c>
       <c r="F23" s="3">
         <v>-9200</v>
@@ -1185,8 +1185,8 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>3</v>
@@ -1252,10 +1252,10 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-16100</v>
+        <v>-17300</v>
       </c>
       <c r="E26" s="3">
-        <v>-22500</v>
+        <v>-22200</v>
       </c>
       <c r="F26" s="3">
         <v>-9200</v>
@@ -1351,10 +1351,10 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3900</v>
+        <v>-3800</v>
       </c>
       <c r="E32" s="3">
         <v>-8900</v>
@@ -1650,7 +1650,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2900</v>
+        <v>2700</v>
       </c>
       <c r="E41" s="3">
         <v>2400</v>
@@ -1716,10 +1716,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3400</v>
+        <v>2400</v>
       </c>
       <c r="E43" s="3">
-        <v>2100</v>
+        <v>1800</v>
       </c>
       <c r="F43" s="3">
         <v>4000</v>
@@ -1749,10 +1749,10 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E44" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F44" s="3">
         <v>300</v>
@@ -1781,11 +1781,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>2300</v>
       </c>
       <c r="E45" s="3">
-        <v>1700</v>
+        <v>2600</v>
       </c>
       <c r="F45" s="3">
         <v>1300</v>
@@ -1881,10 +1881,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>20600</v>
+        <v>800</v>
       </c>
       <c r="E48" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="F48" s="3">
         <v>1700</v>
@@ -1914,10 +1914,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7400</v>
+        <v>7100</v>
       </c>
       <c r="E49" s="3">
-        <v>3100</v>
+        <v>2900</v>
       </c>
       <c r="F49" s="3">
         <v>4100</v>
@@ -2012,11 +2012,11 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>300</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2142,10 +2142,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7200</v>
+        <v>6200</v>
       </c>
       <c r="E57" s="3">
-        <v>10500</v>
+        <v>10300</v>
       </c>
       <c r="F57" s="3">
         <v>3900</v>
@@ -2175,10 +2175,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>12600</v>
+        <v>11700</v>
       </c>
       <c r="E58" s="3">
-        <v>15800</v>
+        <v>15700</v>
       </c>
       <c r="F58" s="3">
         <v>14400</v>
@@ -2208,10 +2208,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>10800</v>
+        <v>13600</v>
       </c>
       <c r="E59" s="3">
-        <v>5100</v>
+        <v>5800</v>
       </c>
       <c r="F59" s="3">
         <v>1200</v>
@@ -2274,10 +2274,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1400</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1500</v>
       </c>
       <c r="F61" s="3">
         <v>1500</v>
@@ -2307,10 +2307,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E62" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>3</v>
@@ -2903,10 +2903,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="F83" s="3">
         <v>500</v>
@@ -3101,10 +3101,10 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-9800</v>
+        <v>-7400</v>
       </c>
       <c r="E89" s="3">
-        <v>-6000</v>
+        <v>-6700</v>
       </c>
       <c r="F89" s="3">
         <v>-4600</v>
@@ -3494,10 +3494,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>500</v>
+        <v>2900</v>
       </c>
       <c r="E102" s="3">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="F102" s="3">
         <v>-800</v>
